--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AJ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,22 +542,22 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Department_Requestor</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Additional_Comments_Information</t>
+          <t>Additional_Comments</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Threshold_Accept</t>
+          <t>Threshold</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Goal_Design_Target</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
@@ -567,45 +567,35 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>Co_Deliver_Team_Member</t>
+          <t>Accept_Goal</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>Accept_Goal</t>
+          <t>Applicable_SKUs</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>Committed_to_Deliver_by</t>
+          <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>Applicable_SKUs</t>
+          <t>Ambiguity_Flag</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>Cleaned_Requirement_Text</t>
+          <t>Reason_for_Ambiguity</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>Ambiguity_Flag</t>
+          <t>Comment</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
-        <is>
-          <t>Reason_for_Ambiguity</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -739,17 +729,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Is there a reason to have 3 names for the same reference ?
-HP OJP 9010 All-in-one Printer series
-HP OJP 9010e All-in-One Printer series
-HP OJP 9010 All-in-One Printer
-Have too many names isn't efficient and can induce user errors</t>
+          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>two names / reference are proposed
-currently 4 references for Office Jet Pro 9010</t>
+          <t>two names / reference are proposed currently 4 references for Office Jet Pro 9010</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -762,31 +747,29 @@
           <t>Solution</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr"/>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>The number of product reference names shown to customers on 123.hp.com for OfficeJet Pro 9010 series should be reduced to a single, consistent name to prevent user confusion and errors.</t>
+        </is>
+      </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>For the OfficeJet Pro 9010 printer, ensure that only one product name/reference is presented to customers on all interfaces, eliminating duplicate or confusing naming.</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
           <t>NO</t>
         </is>
       </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -923,31 +906,29 @@
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr"/>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>The printer must reliably print on all new and current EM (Evaluation Media) and market segment media types, meeting intervention specifications and climatic conditions as defined for the Manhattan platform.</t>
+        </is>
+      </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>The printer must operate reliably and meet minimum print quality (PQ) standards for all new and current EM (Evaluation Media) and market segment media across all regions and climatic conditions.</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
           <t>NO</t>
         </is>
       </c>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1084,31 +1065,29 @@
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr"/>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>The printer must function correctly without hardware failure, specifically the input tray sensor flag, when placed and operated on uneven surfaces such as sofas, table cloths, or carpets.</t>
+        </is>
+      </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>The product must function properly and without hardware failure (e.g., input tray sensor flag breakage) when placed and operated on uneven surfaces such as sofas, table cloths, or carpets.</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
           <t>NO</t>
         </is>
       </c>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1254,31 +1233,29 @@
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>The printer should not experience functional failure when tilted left or right by up to 20 degrees during printing.</t>
+        </is>
+      </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Assess whether the printer experiences any functional failures when tilted left and right up to 20 degrees during operation (printing).</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
           <t>NO</t>
         </is>
       </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1427,31 +1404,29 @@
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr"/>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>The printer must print without print quality issues when operated on a trolley.</t>
+        </is>
+      </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>The printer must print without print quality (PQ) issues when placed and operated on a trolley.</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
           <t>NO</t>
         </is>
       </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,189 +425,199 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ6"/>
+  <dimension ref="A1:AL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>CMWS
 EMWS</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Requestor </t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Department (Requestor)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Marconi SF(Non-PDL)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Marconi SF PDL</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Marconi Base</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Marconi PDL Base Specific</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Marconi Hi</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Marconi PDL Hi Specific</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Additional Comments/Information</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Threshold
 (Accept)</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Goal
 (Design Target)</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Lead Function</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Lead</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Co Deliver Team Member</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Accept - Goal</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Committed to Deliver by </t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Requestor</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Additional_Comments</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Threshold</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>Goal</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Department_Requestor</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Additional_Comments_Information</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Threshold_Accept</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Goal_Design_Target</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Lead_Function</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Co_Deliver_Team_Member</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Accept_Goal</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Committed_to_Deliver_by</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -729,12 +751,17 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series HP OJP 9010e All-in-One Printer series HP OJP 9010 All-in-One Printer Have too many names isn't efficient and can induce user errors</t>
+          <t>Is there a reason to have 3 names for the same reference ?
+HP OJP 9010 All-in-one Printer series
+HP OJP 9010e All-in-One Printer series
+HP OJP 9010 All-in-One Printer
+Have too many names isn't efficient and can induce user errors</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>two names / reference are proposed currently 4 references for Office Jet Pro 9010</t>
+          <t>two names / reference are proposed
+currently 4 references for Office Jet Pro 9010</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -747,29 +774,31 @@
           <t>Solution</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Drop</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>The number of product reference names shown to customers on 123.hp.com for OfficeJet Pro 9010 series should be reduced to a single, consistent name to prevent user confusion and errors.</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Reduce the number of product name references for OfficeJet Pro 9010 series shown to customers on 123.hp.com to a maximum of one, to avoid confusion and user error.</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,29 +935,31 @@
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>Accept - Threshold</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>The printer must reliably print on all new and current EM (Evaluation Media) and market segment media types, meeting intervention specifications and climatic conditions as defined for the Manhattan platform.</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Printer must reliably print on all new and current EM (Evaluation Media) and market segment media types, meeting minimum print quality standards by region and intervention specifications for all climatic conditions relevant to the Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1065,29 +1096,31 @@
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
         <is>
           <t>Accept - Threshold</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>The printer must function correctly without hardware failure, specifically the input tray sensor flag, when placed and operated on uneven surfaces such as sofas, table cloths, or carpets.</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>The product must function correctly and without breaking the input tray sensor flag when placed and operated on uneven surfaces such as sofas, table cloths, or carpets.</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1233,29 +1266,31 @@
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
         <is>
           <t>Drop</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>The printer should not experience functional failure when tilted left or right by up to 20 degrees during printing.</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Assess whether the printer experiences any functional failures when tilted left and right up to 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1404,29 +1439,31 @@
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr">
         <is>
           <t>Accept - Threshold</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>The printer must print without print quality issues when operated on a trolley.</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>The printer must maintain print quality and proper operation when placed on a trolley and printing.</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,70 +554,35 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Department_Requestor</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Additional_Comments_Information</t>
+          <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Threshold_Accept</t>
+          <t>Applicable_SKUs</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Goal_Design_Target</t>
+          <t>Ambiguity_Flag</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Lead_Function</t>
+          <t>Reason_for_Ambiguity</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Co_Deliver_Team_Member</t>
+          <t>Comment</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Accept_Goal</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>Committed_to_Deliver_by</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Applicable_SKUs</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Cleaned_Requirement_Text</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>Ambiguity_Flag</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>Reason_for_Ambiguity</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -751,54 +716,22 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Is there a reason to have 3 names for the same reference ?
-HP OJP 9010 All-in-one Printer series
-HP OJP 9010e All-in-One Printer series
-HP OJP 9010 All-in-One Printer
-Have too many names isn't efficient and can induce user errors</t>
+          <t>Reduce the number of naming references for the HP OfficeJet Pro 9010 series on 123.hp.com to a single, consistent name to avoid user confusion.</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>two names / reference are proposed
-currently 4 references for Office Jet Pro 9010</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Only one name / reference is proposed to customer</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Solution</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Reduce the number of product name references for OfficeJet Pro 9010 series shown to customers on 123.hp.com to a maximum of one, to avoid confusion and user error.</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -917,49 +850,22 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+          <t>Printer must reliably operate with all new and current EM (Evaluation Media) and market segment media, meeting intervention specifications across all relevant climatic conditions for the Manhattan platform.</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Minimum PQ acceptable by region</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Pass intervention rate and NO PQ issue</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Printer must reliably print on all new and current EM (Evaluation Media) and market segment media types, meeting minimum print quality standards by region and intervention specifications for all climatic conditions relevant to the Manhattan platform.</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1078,49 +984,22 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+          <t>The printer must operate normally and without hardware failure when placed on uneven surfaces such as sofas, table cloths, and carpets.</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer requirement </t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>The product must function correctly and without breaking the input tray sensor flag when placed and operated on uneven surfaces such as sofas, table cloths, or carpets.</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1248,49 +1127,22 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+          <t>Assess whether the printer experiences any functional failure when tilted 20 degrees left and right during printing.</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Assess whether the printer experiences any functional failures when tilted left and right up to 20 degrees during printing.</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1421,49 +1273,22 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>To check if there is PQ issue when printer print on trolley.</t>
+          <t>The printer must maintain print quality and function correctly when printing while placed on a moving trolley.</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>The printer must maintain print quality and proper operation when placed on a trolley and printing.</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,35 +554,70 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Department_Requestor</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
+          <t>Additional_Comments_Information</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Threshold_Accept</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Goal_Design_Target</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Lead_Function</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Co_Deliver_Team_Member</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Accept_Goal</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Committed_to_Deliver_by</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Applicable_SKUs</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Applicable_SKUs</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -716,22 +751,54 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Reduce the number of naming references for the HP OfficeJet Pro 9010 series on 123.hp.com to a single, consistent name to avoid user confusion.</t>
+          <t>Is there a reason to have 3 names for the same reference ?
+HP OJP 9010 All-in-one Printer series
+HP OJP 9010e All-in-One Printer series
+HP OJP 9010 All-in-One Printer
+Have too many names isn't efficient and can induce user errors</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
+          <t>two names / reference are proposed
+currently 4 references for Office Jet Pro 9010</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Only one name / reference is proposed to customer</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>The product naming convention on 123.hp.com must be consolidated so that only one name/reference is presented to the customer for the HP OfficeJet Pro 9010 series, to reduce confusion and user errors.</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -850,22 +917,49 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Printer must reliably operate with all new and current EM (Evaluation Media) and market segment media, meeting intervention specifications across all relevant climatic conditions for the Manhattan platform.</t>
+          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
+          <t>Minimum PQ acceptable by region</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Pass intervention rate and NO PQ issue</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>The printer must reliably print on all new and current EM (Evaluation Media) and market segment media, meeting the intervention specifications for different media and climatic conditions as defined for the Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,22 +1078,49 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>The printer must operate normally and without hardware failure when placed on uneven surfaces such as sofas, table cloths, and carpets.</t>
+          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Meet customer requirement </t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>The printer must operate correctly when placed on uneven surfaces (such as sofas, table cloths, or carpets) without causing failure or breakage of input tray sensor components.</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1127,22 +1248,49 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Assess whether the printer experiences any functional failure when tilted 20 degrees left and right during printing.</t>
+          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>The printer must not experience functional failures when tilted 20 degrees to the left or right during printing.</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1273,22 +1421,49 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>The printer must maintain print quality and function correctly when printing while placed on a moving trolley.</t>
+          <t>To check if there is PQ issue when printer print on trolley.</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>The printer must be able to print while placed on a trolley without causing any print quality issues.</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -559,57 +559,57 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
+          <t>Applicable_SKUs</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Cleaned_Requirement_Text</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Ambiguity_Flag</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Reason_for_Ambiguity</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>Additional_Comments_Information</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Threshold_Accept</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Goal_Design_Target</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Lead_Function</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Co_Deliver_Team_Member</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Accept_Goal</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Committed_to_Deliver_by</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Applicable_SKUs</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Cleaned_Requirement_Text</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>Ambiguity_Flag</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>Reason_for_Ambiguity</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
@@ -751,49 +751,44 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Is there a reason to have 3 names for the same reference ?
-HP OJP 9010 All-in-one Printer series
-HP OJP 9010e All-in-One Printer series
-HP OJP 9010 All-in-One Printer
-Have too many names isn't efficient and can induce user errors</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>two names / reference are proposed
-currently 4 references for Office Jet Pro 9010</t>
+          <t>Reduce the number of reference names for OfficeJet Pro 9010 series printers on 123.hp.com to a maximum of two to minimize user confusion and errors.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Only one name / reference is proposed to customer</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series, HP OJP 9010e All-in-One Printer series, HP OJP 9010 All-in-One Printer. Have too many names isn't efficient and can induce user errors</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Two names/reference are proposed; currently 4 references for Office Jet Pro 9010</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Only one name/reference is proposed to customer</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>Solution</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr">
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>Drop</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>The product naming convention on 123.hp.com must be consolidated so that only one name/reference is presented to the customer for the HP OfficeJet Pro 9010 series, to reduce confusion and user errors.</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>NO</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr"/>
@@ -917,44 +912,44 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Printer must be able to operate with all new and current EM (Evaluation Media) and market segment media, meeting intervention specifications for different media and climatic conditions on the Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
           <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>Minimum PQ acceptable by region</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>Pass intervention rate and NO PQ issue</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr">
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>The printer must reliably print on all new and current EM (Evaluation Media) and market segment media, meeting the intervention specifications for different media and climatic conditions as defined for the Manhattan platform.</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>NO</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr"/>
@@ -1078,44 +1073,44 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>The printer must function properly without hardware failure when placed and operated on uneven surfaces such as sofas, table cloths, and carpets.</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
           <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t xml:space="preserve">Meet customer requirement </t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t xml:space="preserve">Meet customer  requirement </t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr">
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>The printer must operate correctly when placed on uneven surfaces (such as sofas, table cloths, or carpets) without causing failure or breakage of input tray sensor components.</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>NO</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr"/>
@@ -1248,44 +1243,44 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Assess whether the printer experiences any functional failure if tilted 20 degrees to the left or right during printing.</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
           <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t xml:space="preserve">Meet customer  requirement </t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t xml:space="preserve">Meet customer  requirement </t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr">
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>Drop</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>The printer must not experience functional failures when tilted 20 degrees to the left or right during printing.</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>NO</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr"/>
@@ -1421,44 +1416,44 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>The printer must print without print quality issues when placed and operated on a trolley.</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
           <t>To check if there is PQ issue when printer print on trolley.</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t xml:space="preserve">Meet customer  requirement </t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t xml:space="preserve">Meet customer  requirement </t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>ME Platform</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr">
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>The printer must be able to print while placed on a trolley without causing any print quality issues.</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>NO</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -559,57 +559,57 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
+          <t>Additional_Comments_Information</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Threshold_Accept</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Goal_Design_Target</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Lead_Function</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Co_Deliver_Team_Member</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Accept_Goal</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Committed_to_Deliver_by</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
           <t>Applicable_SKUs</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Ambiguity_Flag</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Reason_for_Ambiguity</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Additional_Comments_Information</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Threshold_Accept</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>Goal_Design_Target</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Lead_Function</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Co_Deliver_Team_Member</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>Accept_Goal</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>Committed_to_Deliver_by</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
@@ -751,44 +751,49 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
+          <t>Is there a reason to have 3 names for the same reference ?
+HP OJP 9010 All-in-one Printer series
+HP OJP 9010e All-in-One Printer series
+HP OJP 9010 All-in-One Printer
+Have too many names isn't efficient and can induce user errors</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>two names / reference are proposed
+currently 4 references for Office Jet Pro 9010</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Only one name / reference is proposed to customer</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Solution</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Reduce the number of reference names for OfficeJet Pro 9010 series printers on 123.hp.com to a maximum of two to minimize user confusion and errors.</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>For the OfficeJet Pro 9010 series, ensure only one reference name is presented to customers on 123.hp.com to minimize confusion and user errors.</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>NO</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Is there a reason to have 3 names for the same reference ? HP OJP 9010 All-in-one Printer series, HP OJP 9010e All-in-One Printer series, HP OJP 9010 All-in-One Printer. Have too many names isn't efficient and can induce user errors</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Two names/reference are proposed; currently 4 references for Office Jet Pro 9010</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>Only one name/reference is proposed to customer</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>Solution</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Drop</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr"/>
@@ -912,44 +917,44 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
+          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Minimum PQ acceptable by region</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Pass intervention rate and NO PQ issue</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Printer must be able to operate with all new and current EM (Evaluation Media) and market segment media, meeting intervention specifications for different media and climatic conditions on the Manhattan platform.</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Printer must be able to reliably print on all new and current EM (Evaluation Media) and market segment media types, meeting regional print quality (PQ) and intervention specifications under all relevant climatic conditions.</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>NO</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Minimum PQ acceptable by region</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>Pass intervention rate and NO PQ issue</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr"/>
@@ -1073,44 +1078,44 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
+          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer requirement </t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>The printer must function properly without hardware failure when placed and operated on uneven surfaces such as sofas, table cloths, and carpets.</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Printer must operate reliably without component failure (e.g., input tray sensor flag) when placed and used on uneven surfaces such as sofas, table cloths, or carpets.</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>NO</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer requirement </t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr"/>
@@ -1243,44 +1248,44 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
+          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Assess whether the printer experiences any functional failure if tilted 20 degrees to the left or right during printing.</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Assess printer functionality and reliability when tilted 20 degrees left and right during printing, ensuring no functional failure occurs.</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>NO</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Drop</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr"/>
@@ -1416,44 +1421,44 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
+          <t>To check if there is PQ issue when printer print on trolley.</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meet customer  requirement </t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ME Platform</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr">
+        <is>
           <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>The printer must print without print quality issues when placed and operated on a trolley.</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Printer must maintain acceptable print quality when printing while placed on a moving or stationary trolley.</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>NO</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>To check if there is PQ issue when printer print on trolley.</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr"/>

--- a/consolidation/output/refactored_old_prd.xlsx
+++ b/consolidation/output/refactored_old_prd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,70 +554,35 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Department_Requestor</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Additional_Comments_Information</t>
+          <t>Applicable_SKUs</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Threshold_Accept</t>
+          <t>Cleaned_Requirement_Text</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Goal_Design_Target</t>
+          <t>Ambiguity_Flag</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Lead_Function</t>
+          <t>Reason_for_Ambiguity</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Co_Deliver_Team_Member</t>
+          <t>Comment</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Accept_Goal</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>Committed_to_Deliver_by</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Applicable_SKUs</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Cleaned_Requirement_Text</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>Ambiguity_Flag</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>Reason_for_Ambiguity</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Verification_Status</t>
         </is>
@@ -751,54 +716,22 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Is there a reason to have 3 names for the same reference ?
-HP OJP 9010 All-in-one Printer series
-HP OJP 9010e All-in-One Printer series
-HP OJP 9010 All-in-One Printer
-Have too many names isn't efficient and can induce user errors</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>two names / reference are proposed
-currently 4 references for Office Jet Pro 9010</t>
+          <t>Reduce the number of product reference names shown to customers during the Out-Of-Box Experience (OOBE) at 123.hp.com for the HP OfficeJet Pro 9010 series to a single, consistent name.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Only one name / reference is proposed to customer</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Solution</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>For the OfficeJet Pro 9010 series, ensure only one reference name is presented to customers on 123.hp.com to minimize confusion and user errors.</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -917,49 +850,22 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Printer to meet intervention spec for the different media and climatic conditions for Manhattan platform.</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Minimum PQ acceptable by region</t>
+          <t>Printer must reliably operate and meet intervention specifications for all new and current EM (Evaluation Media) and market segment media under various climatic conditions for the Manhattan platform.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Pass intervention rate and NO PQ issue</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Printer must be able to reliably print on all new and current EM (Evaluation Media) and market segment media types, meeting regional print quality (PQ) and intervention specifications under all relevant climatic conditions.</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1078,49 +984,22 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>As the complain on Vasari , input tray sensor flag broken when printer is placed on uneven surfact , this issue should be fixed in new product</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer requirement </t>
+          <t>The printer must function correctly and without hardware failure when placed and operated on uneven surfaces such as sofas, table cloths, or carpets.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Printer must operate reliably without component failure (e.g., input tray sensor flag) when placed and used on uneven surfaces such as sofas, table cloths, or carpets.</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1248,49 +1127,22 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>To assess whether there is any functional failure if customer tilt the printer during printing.(Sayan tilt left and right each at 20 degree while printing )</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
+          <t>Assess printer functionality for failures when the device is tilted 20 degrees left and right during printing.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>Drop</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Assess printer functionality and reliability when tilted 20 degrees left and right during printing, ensuring no functional failure occurs.</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1421,49 +1273,22 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>To check if there is PQ issue when printer print on trolley.</t>
+          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
+          <t>The printer must maintain print quality and function correctly when printing while placed on a trolley.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meet customer  requirement </t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ME Platform</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>Accept - Threshold</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>['Marconi SF(Non-PDL)', 'Marconi SF PDL', 'Marconi Base', 'Marconi PDL Base Specific', 'Marconi Hi', 'Marconi PDL Hi Specific']</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Printer must maintain acceptable print quality when printing while placed on a moving or stationary trolley.</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
